--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,15 +43,20 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="006B21A8"/>
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="00555577"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +80,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00F5F5F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -130,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,7 +525,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Max Score  |  Week of 2026-05-04</t>
+          <t>Courtside  |  Max Score  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -525,43 +538,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -578,10 +591,10 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Anmol Sharma
-25% pred | 25% hist
-[INCLUDE]</t>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -589,7 +602,7 @@
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -597,20 +610,20 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Bret Saldanha
-20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -618,20 +631,20 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-46% pred | 46% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -639,12 +652,12 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Karanvir Bhatia
 20% pred | 0% hist
-[INCLUDE]</t>
+[]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
@@ -679,7 +692,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-04</t>
+          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -692,43 +705,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -745,10 +758,10 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Bret Saldanha
-25% pred | 25% hist
-[INCLUDE]</t>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -756,7 +769,7 @@
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -764,20 +777,20 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Richard D'Costa
-49% pred | 49% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+Atulan Purohit
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -785,20 +798,20 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Anmol Sharma
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
 20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+[]</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -806,12 +819,12 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anmol Sharma
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Karanvir Bhatia
 20% pred | 0% hist
-[INCLUDE]</t>
+[]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
@@ -846,7 +859,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Class Variety  |  Week of 2026-05-04</t>
+          <t>Courtside  |  Class Variety  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -859,43 +872,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -912,10 +925,10 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Bret Saldanha
-25% pred | 25% hist
-[INCLUDE]</t>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -923,7 +936,7 @@
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -931,20 +944,20 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Richard D'Costa
-49% pred | 49% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+Atulan Purohit
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -952,20 +965,20 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karan Bhatia
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
 20% pred | 0% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+[]</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -973,12 +986,12 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anmol Sharma
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Karanvir Bhatia
 20% pred | 0% hist
-[INCLUDE]</t>
+[]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -43,10 +43,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <color rgb="006B21A8"/>
       <sz val="9"/>
     </font>
@@ -54,6 +50,10 @@
       <b val="1"/>
       <color rgb="00555577"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -80,17 +80,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -139,10 +139,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -591,18 +591,18 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
+          <t>Cardio Barre
+Raunak Khemuka
+25% pred | 25% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -610,20 +610,20 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Atulan Purohit
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n"/>
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -631,20 +631,20 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>FIT
-Mrigakshi Jaiswal
+Bret Saldanha
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -652,15 +652,36 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Karanvir Bhatia
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -676,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -758,10 +779,10 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Mat 57
-Reshma Sharma
+          <t>FIT
+Raunak Khemuka
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -769,7 +790,7 @@
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -777,20 +798,20 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Atulan Purohit
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n"/>
+Pranjali Jain
+46% pred | 46% hist
+[CONSIDER]</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -798,20 +819,20 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+29% pred | 29% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -819,15 +840,36 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Express
-Karanvir Bhatia
+Pranjali Jain
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -843,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -925,18 +967,18 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
+          <t>Cardio Barre
+Raunak Khemuka
+25% pred | 25% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -944,20 +986,20 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Atulan Purohit
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n"/>
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -965,20 +1007,20 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>FIT
-Mrigakshi Jaiswal
+Bret Saldanha
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -986,15 +1028,36 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Karanvir Bhatia
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Mrigakshi Jaiswal
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -525,7 +525,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Max Score  |  Week of 2026-05-11</t>
+          <t>Courtside  |  Max Score  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -538,43 +538,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -600,9 +600,9 @@
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -614,7 +614,7 @@
       <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Mrigakshi Jaiswal
+Atulan Purohit
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -655,7 +655,7 @@
       <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
+Cauveri Vikrant
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -713,7 +713,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-11</t>
+          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -726,50 +726,50 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -779,18 +779,18 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+          <t>Barre 57 Express
+Mrigakshi Jaiswal
+20% pred | 20% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>11:30</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -801,10 +801,10 @@
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Pranjali Jain
-46% pred | 46% hist
-[CONSIDER]</t>
+          <t>Cardio Barre Express
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -821,10 +821,10 @@
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Simran Dutt
-29% pred | 29% hist
-[CONSIDER]</t>
+          <t>FIT
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
@@ -840,9 +840,9 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
 Reshma Sharma
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
@@ -861,10 +861,10 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Pranjali Jain
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Rohan Dahima
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -901,7 +901,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Class Variety  |  Week of 2026-05-11</t>
+          <t>Courtside  |  Class Variety  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -914,43 +914,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -967,18 +967,18 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>FIT
 Raunak Khemuka
-25% pred | 25% hist
-[CONSIDER]</t>
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -1009,10 +1009,10 @@
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+          <t>Barre 57
+Simran Dutt
+29% pred | 29% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
@@ -1028,10 +1028,10 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Cauveri Vikrant
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -1049,10 +1049,10 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Mrigakshi Jaiswal
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Reshma Sharma
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -525,7 +525,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Max Score  |  Week of 2026-05-04</t>
+          <t>Courtside  |  Max Score  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -538,43 +538,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -614,9 +614,9 @@
       <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+Pranjali Jain
+46% pred | 46% hist
+[CONSIDER]</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Cauveri Vikrant
+Reshma Sharma
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -676,7 +676,7 @@
       <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
-Reshma Sharma
+Rohan Dahima
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -713,7 +713,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-04</t>
+          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -726,50 +726,50 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -779,18 +779,18 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Barre 57 Express
-Mrigakshi Jaiswal
-20% pred | 20% hist
+          <t>Cardio Barre
+Raunak Khemuka
+25% pred | 25% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -801,10 +801,10 @@
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+          <t>Barre 57
+Pranjali Jain
+46% pred | 46% hist
+[CONSIDER]</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Reshma Sharma
+Rohan Dahima
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -864,7 +864,7 @@
       <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
-Rohan Dahima
+Reshma Sharma
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -901,7 +901,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Class Variety  |  Week of 2026-05-04</t>
+          <t>Courtside  |  Class Variety  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -914,43 +914,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -967,10 +967,10 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Cardio Barre
 Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+25% pred | 25% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -978,7 +978,7 @@
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -990,9 +990,9 @@
       <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+Karan Bhatia
+29% pred | 29% hist
+[CONSIDER]</t>
         </is>
       </c>
     </row>
@@ -1009,10 +1009,10 @@
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Simran Dutt
-29% pred | 29% hist
-[CONSIDER]</t>
+          <t>FIT
+Bret Saldanha
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
@@ -1028,10 +1028,10 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Cauveri Vikrant
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Rohan Dahima
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -1049,10 +1049,10 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Reshma Sharma
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Mrigakshi Jaiswal
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -602,7 +602,7 @@
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -614,9 +614,9 @@
       <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Pranjali Jain
-46% pred | 46% hist
-[CONSIDER]</t>
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -802,9 +802,9 @@
       <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Pranjali Jain
-46% pred | 46% hist
-[CONSIDER]</t>
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -840,10 +840,10 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -861,10 +861,10 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Reshma Sharma
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -1031,7 +1031,7 @@
       <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
+Reshma Sharma
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -1052,7 +1052,7 @@
       <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Mat 57 Express
-Mrigakshi Jaiswal
+Rohan Dahima
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -43,6 +43,10 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="006B21A8"/>
       <sz val="9"/>
     </font>
@@ -50,10 +54,6 @@
       <b val="1"/>
       <color rgb="00555577"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -80,17 +80,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -139,10 +139,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -525,7 +525,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Max Score  |  Week of 2026-05-11</t>
+          <t>Courtside  |  Max Score  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -538,43 +538,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -591,10 +591,10 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Raunak Khemuka
-25% pred | 25% hist
-[CONSIDER]</t>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -602,7 +602,7 @@
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -611,12 +611,12 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+Rohan Dahima
+49% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+33% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
@@ -652,18 +652,18 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
+[]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
@@ -673,12 +673,12 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Rohan Dahima
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Karanvir Bhatia
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
+[]</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>
@@ -713,7 +713,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-11</t>
+          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -726,43 +726,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -779,10 +779,10 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Raunak Khemuka
-25% pred | 25% hist
-[CONSIDER]</t>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -790,7 +790,7 @@
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -799,12 +799,12 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+Rohan Dahima
+49% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+33% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
@@ -840,18 +840,18 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
+[]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
@@ -861,12 +861,12 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Karanvir Bhatia
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
+[]</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>
@@ -901,7 +901,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Class Variety  |  Week of 2026-05-11</t>
+          <t>Courtside  |  Class Variety  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -914,43 +914,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -967,10 +967,10 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Raunak Khemuka
-25% pred | 25% hist
-[CONSIDER]</t>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -978,7 +978,7 @@
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -987,12 +987,12 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Barre 57
-Karan Bhatia
-29% pred | 29% hist
-[CONSIDER]</t>
+Rohan Dahima
+49% pred | 0% hist
+[]</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Bret Saldanha
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57
+Vivaran Dhasmana
+33% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
@@ -1028,18 +1028,18 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Reshma Sharma
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
+[]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
@@ -1049,12 +1049,12 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Rohan Dahima
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Karanvir Bhatia
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
+[]</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -43,10 +43,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <color rgb="006B21A8"/>
       <sz val="9"/>
     </font>
@@ -54,6 +50,10 @@
       <b val="1"/>
       <color rgb="00555577"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -80,17 +80,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -139,10 +139,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -525,7 +525,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Max Score  |  Week of 2026-05-04</t>
+          <t>Courtside  |  Max Score  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -538,43 +538,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -591,18 +591,18 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
+          <t>Barre 57 Express
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>10:15</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -611,12 +611,12 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-49% pred | 0% hist
-[]</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-33% pred | 0% hist
-[]</t>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
@@ -652,18 +652,18 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pranjali Jain
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
@@ -673,12 +673,12 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Karanvir Bhatia
-20% pred | 0% hist
-[]</t>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>
@@ -713,7 +713,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-04</t>
+          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -726,50 +726,50 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -779,18 +779,18 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
+          <t>Barre 57
+Karanvir Bhatia
+36% pred | 36% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>10:15</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -799,12 +799,12 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Rohan Dahima
-49% pred | 0% hist
-[]</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-33% pred | 0% hist
-[]</t>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
@@ -840,18 +840,18 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
@@ -861,12 +861,12 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Karanvir Bhatia
-20% pred | 0% hist
-[]</t>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Richard D'Costa
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>
@@ -901,7 +901,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Class Variety  |  Week of 2026-05-04</t>
+          <t>Courtside  |  Class Variety  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -914,50 +914,50 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -967,18 +967,18 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Mat 57
-Reshma Sharma
-20% pred | 0% hist
-[]</t>
+          <t>Barre 57
+Karanvir Bhatia
+36% pred | 36% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>10:15</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -987,19 +987,19 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Rohan Dahima
-49% pred | 0% hist
-[]</t>
+Simonelle De Vitre
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -1007,12 +1007,12 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57
-Vivaran Dhasmana
-33% pred | 0% hist
-[]</t>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
@@ -1020,7 +1020,7 @@
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -1028,20 +1028,20 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>FIT
-Mrigakshi Jaiswal
-20% pred | 0% hist
-[]</t>
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
@@ -1049,12 +1049,12 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Karanvir Bhatia
-20% pred | 0% hist
-[]</t>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Pranjali Jain
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -47,13 +47,13 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00555577"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -85,12 +85,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F8"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00F5F5F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -139,10 +139,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Max Score  |  Week of 2026-05-11</t>
+          <t>Courtside  |  Max Score  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -538,50 +538,50 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -589,20 +589,20 @@
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="n"/>
+37% pred | 37% hist
+[INCLUDE]</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -610,11 +610,18 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Simonelle De Vitre
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Atulan Purohit
+44% pred | 44% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Karanvir Bhatia
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -640,48 +647,6 @@
         </is>
       </c>
       <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pranjali Jain
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -697,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -713,7 +678,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-11</t>
+          <t>Courtside  |  Trainer Hours  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -726,50 +691,50 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -780,17 +745,17 @@
       <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Karanvir Bhatia
-36% pred | 36% hist
-[CONSIDER]</t>
+Pranjali Jain
+62% pred | 62% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -801,17 +766,17 @@
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
-Cauveri Vikrant
+          <t>FIT
+Rohan Dahima
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -819,20 +784,20 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anmol Sharma
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
+Karanvir Bhatia
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -840,36 +805,15 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Reshma Sharma
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Cauveri Vikrant
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Richard D'Costa
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -885,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -901,7 +845,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Courtside  |  Class Variety  |  Week of 2026-05-11</t>
+          <t>Courtside  |  Class Variety  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -914,43 +858,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -965,20 +909,20 @@
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karanvir Bhatia
-36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Rohan Dahima
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -986,20 +930,20 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Simonelle De Vitre
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+Atulan Purohit
+44% pred | 44% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>12:30</t>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -1007,15 +951,15 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Express
 Cauveri Vikrant
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1037,27 +981,6 @@
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Pranjali Jain
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,24 +39,19 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0092400E"/>
+      <color rgb="00555577"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="006B21A8"/>
-      <sz val="9"/>
     </font>
     <font>
       <color rgb="000C4A6E"/>
       <sz val="9"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00555577"/>
-      <sz val="10"/>
+      <color rgb="006B21A8"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -70,7 +65,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
+        <fgColor rgb="00F5F5F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,17 +75,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8D5FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F8"/>
+        <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -140,9 +130,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -581,7 +568,7 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -589,20 +576,20 @@
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Raunak Khemuka
-37% pred | 37% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Mat 57
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -610,43 +597,15 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-44% pred | 44% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Karanvir Bhatia
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Pranjali Jain
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -662,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -734,7 +693,7 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -744,10 +703,10 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Pranjali Jain
-62% pred | 62% hist
-[PINNED]</t>
+          <t>Mat 57
+Atulan Purohit
+20% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -755,7 +714,7 @@
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -763,57 +722,15 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Rohan Dahima
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Pranjali Jain
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Karanvir Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
+[]</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -829,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -901,7 +818,7 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -909,20 +826,20 @@
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Mat 57
-Rohan Dahima
+Atulan Purohit
 20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+[]</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -930,57 +847,15 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Atulan Purohit
-44% pred | 44% hist
-[PINNED]</t>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Barre 57 Express
+Pranjali Jain
+20% pred | 0% hist
+[]</t>
         </is>
       </c>
       <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Express
-Cauveri Vikrant
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Anmol Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,15 +43,20 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="006B21A8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <color rgb="000C4A6E"/>
       <sz val="9"/>
     </font>
-    <font>
-      <color rgb="006B21A8"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +80,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00E8D5FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8D5FF"/>
+        <fgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -129,6 +139,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -496,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -568,7 +581,7 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -578,18 +591,18 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Mat 57
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
+          <t>FIT
+Simran Dutt
+51% pred | 51% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -597,15 +610,57 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+23% pred | 23% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+33% pred | 33% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Pranjali Jain
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -621,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -693,7 +748,7 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -703,18 +758,18 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Mat 57
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
+          <t>FIT
+Karan Bhatia
+51% pred | 51% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -722,15 +777,57 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Karan Bhatia
+47% pred | 47% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+33% pred | 33% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Pranjali Jain
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -746,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -818,7 +915,7 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -828,18 +925,18 @@
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Mat 57
-Atulan Purohit
-20% pred | 0% hist
-[]</t>
+          <t>FIT
+Simran Dutt
+51% pred | 51% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
@@ -847,15 +944,57 @@
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+23% pred | 23% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Anmol Sharma
+33% pred | 33% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Pranjali Jain
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -47,13 +47,13 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -85,12 +85,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
   </fills>
@@ -139,10 +139,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -581,70 +581,91 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+36% pred | 36% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Simran Dutt
-51% pred | 51% hist
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+56% pred | 56% hist
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-23% pred | 23% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Anmol Sharma
-33% pred | 33% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>19:00</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -652,15 +673,85 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+18% pred | 18% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+69% pred | 69% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
+40% pred | 40% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -676,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -748,86 +839,170 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+36% pred | 36% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karan Bhatia
-51% pred | 51% hist
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+56% pred | 56% hist
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Karan Bhatia
-47% pred | 47% hist
+      <c r="H4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pranjali Jain
+43% pred | 43% hist
 [INCLUDE]</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Anmol Sharma
-33% pred | 33% hist
-[INCLUDE]</t>
-        </is>
-      </c>
+      <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>19:00</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Rohan Dahima
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Pranjali Jain
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
+Simran Dutt
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+41% pred | 41% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+69% pred | 69% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -843,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -915,70 +1090,91 @@
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Simran Dutt
+36% pred | 36% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Simran Dutt
-51% pred | 51% hist
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Bret Saldanha
+56% pred | 56% hist
 [INCLUDE]</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Karan Bhatia
-23% pred | 23% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>17:45</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Raunak Khemuka
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Anmol Sharma
-33% pred | 33% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>19:00</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -986,15 +1182,85 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Vivaran Dhasmana
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Reshma Sharma
+18% pred | 18% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+69% pred | 69% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pranjali Jain
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
+40% pred | 40% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_courtside.xlsx
+++ b/outputs/schedule_courtside.xlsx
@@ -47,13 +47,13 @@
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -85,12 +85,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -139,10 +139,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -589,8 +589,8 @@
       <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Simran Dutt
-36% pred | 36% hist
+Karan Bhatia
+41% pred | 41% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -621,81 +621,88 @@
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+28% pred | 28% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karanvir Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+69% pred | 69% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Vivaran Dhasmana
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
 Reshma Sharma
-18% pred | 18% hist
-[CONSIDER]</t>
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="D7" s="5" t="n"/>
@@ -703,55 +710,6 @@
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-69% pred | 69% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-40% pred | 40% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -767,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -847,8 +805,8 @@
       <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Simran Dutt
-36% pred | 36% hist
+Karan Bhatia
+41% pred | 41% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -879,17 +837,17 @@
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>11:00</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-43% pred | 43% hist
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+28% pred | 28% hist
 [INCLUDE]</t>
         </is>
       </c>
@@ -911,7 +869,7 @@
       <c r="E6" s="6" t="inlineStr">
         <is>
           <t>FIT
-Rohan Dahima
+Anmol Sharma
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -919,19 +877,19 @@
       <c r="F6" s="6" t="inlineStr">
         <is>
           <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
 Atulan Purohit
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
           <t>FIT
@@ -942,67 +900,32 @@
       </c>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+69% pred | 69% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Reshma Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Simran Dutt
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Mrigakshi Jaiswal
-41% pred | 41% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-69% pred | 69% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1018,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1098,8 +1021,8 @@
       <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Simran Dutt
-36% pred | 36% hist
+Karan Bhatia
+41% pred | 41% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1130,81 +1053,88 @@
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Mrigakshi Jaiswal
+28% pred | 28% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Raunak Khemuka
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Atulan Purohit
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Karanvir Bhatia
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Anmol Sharma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Karanvir Bhatia
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Atulan Purohit
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Cauveri Vikrant
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Mrigakshi Jaiswal
+69% pred | 69% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Vivaran Dhasmana
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
 Reshma Sharma
-18% pred | 18% hist
-[CONSIDER]</t>
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="D7" s="5" t="n"/>
@@ -1212,55 +1142,6 @@
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Mrigakshi Jaiswal
-69% pred | 69% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pranjali Jain
-40% pred | 40% hist
-[INCLUDE]</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Reshma Sharma
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
